--- a/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
+++ b/ABA_mining/outputs/eval/task3/check-in/llama3.2/contrary_v5/EVAL_SUMMARY.xlsx
@@ -541,16 +541,16 @@
         <v>11</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M2" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O2" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
     <row r="3">
@@ -600,16 +600,16 @@
         <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M3" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O3" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
     <row r="4">
@@ -659,16 +659,16 @@
         <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
     </row>
   </sheetData>
@@ -784,16 +784,16 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>0.4048780487804878</v>
+        <v>0.404878</v>
       </c>
       <c r="G2" t="n">
-        <v>0.8829787234042553</v>
+        <v>0.882979</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5551839464882943</v>
+        <v>0.555184</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4722222222222222</v>
+        <v>0.472222</v>
       </c>
       <c r="J2" t="n">
         <v>756</v>
